--- a/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28E8ACD7-B664-4CE8-AF4E-E91EFCB0FD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0F930A3-7DF7-4374-9D45-AF2EE656AD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5428A1EB-020E-4E68-859E-5181B0107EF2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C4291C1A-BBC5-441C-94E6-EAEDEA9195AE}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,2290 +71,2290 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_IN10-765</t>
-  </si>
-  <si>
-    <t>e_w372701897-765</t>
-  </si>
-  <si>
-    <t>g_IN10-765-w372701897-765</t>
+    <t>e_IN10-765_IND</t>
+  </si>
+  <si>
+    <t>e_w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN10-765_IND-w372701897-765_IND</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_IN100-765</t>
-  </si>
-  <si>
-    <t>e_IN101-765</t>
-  </si>
-  <si>
-    <t>g_IN100-765-IN101-765</t>
-  </si>
-  <si>
-    <t>e_IN104-765</t>
-  </si>
-  <si>
-    <t>g_IN101-765-IN104-765</t>
-  </si>
-  <si>
-    <t>e_IN105-765</t>
-  </si>
-  <si>
-    <t>g_IN105-765-IN104-765</t>
-  </si>
-  <si>
-    <t>e_IN136-765</t>
-  </si>
-  <si>
-    <t>g_IN105-765-IN136-765</t>
-  </si>
-  <si>
-    <t>e_IN107-765</t>
-  </si>
-  <si>
-    <t>e_IN94-765</t>
-  </si>
-  <si>
-    <t>g_IN107-765-IN94-765</t>
-  </si>
-  <si>
-    <t>e_IN108-765</t>
-  </si>
-  <si>
-    <t>e_w1077819664-765</t>
-  </si>
-  <si>
-    <t>g_IN108-765-w1077819664-765</t>
-  </si>
-  <si>
-    <t>e_IN116-765</t>
-  </si>
-  <si>
-    <t>e_w1415199647-765</t>
-  </si>
-  <si>
-    <t>g_IN116-765-w1415199647-765</t>
-  </si>
-  <si>
-    <t>e_IN120-765</t>
-  </si>
-  <si>
-    <t>g_IN120-765-w1415199647-765</t>
-  </si>
-  <si>
-    <t>e_IN123-765</t>
-  </si>
-  <si>
-    <t>e_IN121-765</t>
-  </si>
-  <si>
-    <t>g_IN123-765-IN121-765</t>
-  </si>
-  <si>
-    <t>e_IN125-765</t>
-  </si>
-  <si>
-    <t>g_IN123-765-IN125-765</t>
-  </si>
-  <si>
-    <t>e_IN126-765</t>
-  </si>
-  <si>
-    <t>e_IN128-765</t>
-  </si>
-  <si>
-    <t>g_IN126-765-IN128-765</t>
-  </si>
-  <si>
-    <t>e_IN243-765</t>
-  </si>
-  <si>
-    <t>g_IN136-765-IN243-765</t>
-  </si>
-  <si>
-    <t>e_IN137-765</t>
-  </si>
-  <si>
-    <t>e_IN146-765</t>
-  </si>
-  <si>
-    <t>g_IN137-765-IN146-765</t>
-  </si>
-  <si>
-    <t>e_IN139-765</t>
-  </si>
-  <si>
-    <t>e_IN138-765</t>
-  </si>
-  <si>
-    <t>g_IN139-765-IN138-765</t>
-  </si>
-  <si>
-    <t>e_IN142-765</t>
-  </si>
-  <si>
-    <t>e_w311176519-765</t>
-  </si>
-  <si>
-    <t>g_IN142-765-w311176519-765</t>
-  </si>
-  <si>
-    <t>e_w369866141-765</t>
-  </si>
-  <si>
-    <t>g_IN142-765-w369866141-765</t>
-  </si>
-  <si>
-    <t>e_IN148-765</t>
-  </si>
-  <si>
-    <t>e_w1143180503-765</t>
-  </si>
-  <si>
-    <t>g_IN148-765-w1143180503-765</t>
-  </si>
-  <si>
-    <t>e_IN159-765</t>
-  </si>
-  <si>
-    <t>e_IN164-765</t>
-  </si>
-  <si>
-    <t>g_IN159-765-IN164-765</t>
-  </si>
-  <si>
-    <t>e_w686891085-765</t>
-  </si>
-  <si>
-    <t>g_IN159-765-w686891085-765</t>
-  </si>
-  <si>
-    <t>e_IN161-765</t>
-  </si>
-  <si>
-    <t>g_IN161-765-w1143180503-765</t>
-  </si>
-  <si>
-    <t>e_IN163-765</t>
-  </si>
-  <si>
-    <t>g_IN163-765-IN161-765</t>
-  </si>
-  <si>
-    <t>g_IN164-765-IN159-765</t>
-  </si>
-  <si>
-    <t>e_IN187-765</t>
-  </si>
-  <si>
-    <t>g_IN164-765-IN187-765</t>
-  </si>
-  <si>
-    <t>e_IN171-765</t>
-  </si>
-  <si>
-    <t>e_IN174-765</t>
-  </si>
-  <si>
-    <t>g_IN171-765-IN174-765</t>
-  </si>
-  <si>
-    <t>e_IN177-400</t>
-  </si>
-  <si>
-    <t>e_IN176-400</t>
-  </si>
-  <si>
-    <t>g_IN177-400-IN176-400</t>
-  </si>
-  <si>
-    <t>e_IN178-765</t>
-  </si>
-  <si>
-    <t>e_IN175-765</t>
-  </si>
-  <si>
-    <t>g_IN178-765-IN175-765</t>
-  </si>
-  <si>
-    <t>e_IN190-765</t>
-  </si>
-  <si>
-    <t>e_IN183-765</t>
-  </si>
-  <si>
-    <t>g_IN190-765-IN183-765</t>
-  </si>
-  <si>
-    <t>e_IN191-765</t>
-  </si>
-  <si>
-    <t>g_IN191-765-w1143180503-765</t>
-  </si>
-  <si>
-    <t>e_IN196-765</t>
-  </si>
-  <si>
-    <t>g_IN196-765-IN174-765</t>
-  </si>
-  <si>
-    <t>e_IN197-765</t>
-  </si>
-  <si>
-    <t>e_IN194-765</t>
-  </si>
-  <si>
-    <t>g_IN197-765-IN194-765</t>
-  </si>
-  <si>
-    <t>e_IN200-765</t>
-  </si>
-  <si>
-    <t>g_IN200-765-IN196-765</t>
-  </si>
-  <si>
-    <t>e_IN201-765</t>
-  </si>
-  <si>
-    <t>e_IN198-765</t>
-  </si>
-  <si>
-    <t>g_IN201-765-IN198-765</t>
-  </si>
-  <si>
-    <t>e_IN202-765</t>
-  </si>
-  <si>
-    <t>e_IN180-765</t>
-  </si>
-  <si>
-    <t>g_IN202-765-IN180-765</t>
-  </si>
-  <si>
-    <t>e_IN205-765</t>
-  </si>
-  <si>
-    <t>e_IN203-765</t>
-  </si>
-  <si>
-    <t>g_IN205-765-IN203-765</t>
-  </si>
-  <si>
-    <t>e_IN206-765</t>
-  </si>
-  <si>
-    <t>e_w100470285-765</t>
-  </si>
-  <si>
-    <t>g_IN206-765-w100470285-765</t>
-  </si>
-  <si>
-    <t>e_IN218-765</t>
-  </si>
-  <si>
-    <t>e_IN199-765</t>
-  </si>
-  <si>
-    <t>g_IN218-765-IN199-765</t>
-  </si>
-  <si>
-    <t>e_IN222-765</t>
-  </si>
-  <si>
-    <t>e_IN217-765</t>
-  </si>
-  <si>
-    <t>g_IN222-765-IN217-765</t>
-  </si>
-  <si>
-    <t>e_IN225-765</t>
-  </si>
-  <si>
-    <t>g_IN225-765-IN200-765</t>
-  </si>
-  <si>
-    <t>e_IN229-765</t>
-  </si>
-  <si>
-    <t>g_IN229-765-IN225-765</t>
-  </si>
-  <si>
-    <t>e_IN239-765</t>
-  </si>
-  <si>
-    <t>g_IN229-765-IN239-765</t>
-  </si>
-  <si>
-    <t>e_IN230-765</t>
-  </si>
-  <si>
-    <t>e_IN233-765</t>
-  </si>
-  <si>
-    <t>g_IN230-765-IN233-765</t>
-  </si>
-  <si>
-    <t>g_IN230-765-w369866141-765</t>
-  </si>
-  <si>
-    <t>e_IN244-765</t>
-  </si>
-  <si>
-    <t>g_IN233-765-IN244-765</t>
-  </si>
-  <si>
-    <t>e_IN235-400</t>
-  </si>
-  <si>
-    <t>e_w239498664-400</t>
-  </si>
-  <si>
-    <t>g_IN235-400-w239498664-400</t>
-  </si>
-  <si>
-    <t>g_IN239-765-IN229-765</t>
-  </si>
-  <si>
-    <t>e_IN240-765</t>
-  </si>
-  <si>
-    <t>g_IN240-765-IN239-765</t>
-  </si>
-  <si>
-    <t>g_IN244-765-IN233-765</t>
-  </si>
-  <si>
-    <t>e_IN247-765</t>
-  </si>
-  <si>
-    <t>g_IN244-765-IN247-765</t>
-  </si>
-  <si>
-    <t>e_IN246-765</t>
-  </si>
-  <si>
-    <t>e_IN250-765</t>
-  </si>
-  <si>
-    <t>g_IN246-765-IN250-765</t>
-  </si>
-  <si>
-    <t>e_w131484738-765</t>
-  </si>
-  <si>
-    <t>g_IN246-765-w131484738-765</t>
-  </si>
-  <si>
-    <t>e_IN249-765</t>
-  </si>
-  <si>
-    <t>g_IN247-765-IN249-765</t>
-  </si>
-  <si>
-    <t>g_IN249-765-IN247-765</t>
-  </si>
-  <si>
-    <t>g_IN250-765-IN246-765</t>
-  </si>
-  <si>
-    <t>g_IN250-765-IN249-765</t>
-  </si>
-  <si>
-    <t>e_IN253-765</t>
-  </si>
-  <si>
-    <t>e_IN232-765</t>
-  </si>
-  <si>
-    <t>g_IN253-765-IN232-765</t>
-  </si>
-  <si>
-    <t>e_IN254-765</t>
-  </si>
-  <si>
-    <t>g_IN254-765-IN253-765</t>
-  </si>
-  <si>
-    <t>e_IN255-765</t>
-  </si>
-  <si>
-    <t>e_IN257-765</t>
-  </si>
-  <si>
-    <t>g_IN255-765-IN257-765</t>
-  </si>
-  <si>
-    <t>e_IN259-400</t>
-  </si>
-  <si>
-    <t>e_w526897229-400</t>
-  </si>
-  <si>
-    <t>g_IN259-400-w526897229-400</t>
-  </si>
-  <si>
-    <t>e_w93160503-400</t>
-  </si>
-  <si>
-    <t>g_IN259-400-w93160503-400</t>
-  </si>
-  <si>
-    <t>e_IN263-400</t>
-  </si>
-  <si>
-    <t>e_IN262-400</t>
-  </si>
-  <si>
-    <t>g_IN263-400-IN262-400</t>
-  </si>
-  <si>
-    <t>e_IN264-765</t>
-  </si>
-  <si>
-    <t>e_IN270-765</t>
-  </si>
-  <si>
-    <t>g_IN264-765-IN270-765</t>
-  </si>
-  <si>
-    <t>e_IN265-400</t>
-  </si>
-  <si>
-    <t>e_IN260-400</t>
-  </si>
-  <si>
-    <t>g_IN265-400-IN260-400</t>
-  </si>
-  <si>
-    <t>e_IN268-765</t>
-  </si>
-  <si>
-    <t>e_IN258-765</t>
-  </si>
-  <si>
-    <t>g_IN268-765-IN258-765</t>
-  </si>
-  <si>
-    <t>g_IN270-765-IN264-765</t>
-  </si>
-  <si>
-    <t>e_IN272-765</t>
-  </si>
-  <si>
-    <t>g_IN270-765-IN272-765</t>
-  </si>
-  <si>
-    <t>e_IN276-765</t>
-  </si>
-  <si>
-    <t>g_IN272-765-IN276-765</t>
-  </si>
-  <si>
-    <t>e_IN275-765</t>
-  </si>
-  <si>
-    <t>e_IN269-765</t>
-  </si>
-  <si>
-    <t>g_IN275-765-IN269-765</t>
-  </si>
-  <si>
-    <t>g_IN276-765-IN272-765</t>
-  </si>
-  <si>
-    <t>e_IN277-765</t>
-  </si>
-  <si>
-    <t>g_IN276-765-IN277-765</t>
-  </si>
-  <si>
-    <t>e_IN278-765</t>
-  </si>
-  <si>
-    <t>g_IN278-765-IN277-765</t>
-  </si>
-  <si>
-    <t>e_IN279-765</t>
-  </si>
-  <si>
-    <t>e_w607439318-765</t>
-  </si>
-  <si>
-    <t>g_IN279-765-w607439318-765</t>
-  </si>
-  <si>
-    <t>e_IN280-765</t>
-  </si>
-  <si>
-    <t>g_IN280-765-IN279-765</t>
-  </si>
-  <si>
-    <t>e_IN282-765</t>
-  </si>
-  <si>
-    <t>g_IN282-765-IN240-765</t>
-  </si>
-  <si>
-    <t>e_IN284-765</t>
-  </si>
-  <si>
-    <t>g_IN282-765-IN284-765</t>
-  </si>
-  <si>
-    <t>e_IN292-765</t>
-  </si>
-  <si>
-    <t>g_IN284-765-IN292-765</t>
-  </si>
-  <si>
-    <t>e_IN285-400</t>
-  </si>
-  <si>
-    <t>e_IN287-400</t>
-  </si>
-  <si>
-    <t>g_IN285-400-IN287-400</t>
-  </si>
-  <si>
-    <t>e_IN286-400</t>
-  </si>
-  <si>
-    <t>e_w205942950-400</t>
-  </si>
-  <si>
-    <t>g_IN286-400-w205942950-400</t>
-  </si>
-  <si>
-    <t>e_w1012817818-400</t>
-  </si>
-  <si>
-    <t>g_IN287-400-w1012817818-400</t>
-  </si>
-  <si>
-    <t>e_w94199110-400</t>
-  </si>
-  <si>
-    <t>g_IN287-400-w94199110-400</t>
-  </si>
-  <si>
-    <t>e_IN288-765</t>
-  </si>
-  <si>
-    <t>g_IN288-765-IN278-765</t>
-  </si>
-  <si>
-    <t>e_IN289-765</t>
-  </si>
-  <si>
-    <t>g_IN289-765-IN288-765</t>
-  </si>
-  <si>
-    <t>e_IN321-765</t>
-  </si>
-  <si>
-    <t>g_IN289-765-IN321-765</t>
-  </si>
-  <si>
-    <t>e_IN290-400</t>
-  </si>
-  <si>
-    <t>e_w97392607-400</t>
-  </si>
-  <si>
-    <t>g_IN290-400-w97392607-400</t>
-  </si>
-  <si>
-    <t>e_IN295-765</t>
-  </si>
-  <si>
-    <t>g_IN292-765-IN295-765</t>
-  </si>
-  <si>
-    <t>e_IN293-765</t>
-  </si>
-  <si>
-    <t>e_IN283-765</t>
-  </si>
-  <si>
-    <t>g_IN293-765-IN283-765</t>
-  </si>
-  <si>
-    <t>e_w423702239-765</t>
-  </si>
-  <si>
-    <t>g_IN295-765-w423702239-765</t>
-  </si>
-  <si>
-    <t>e_IN298-765</t>
-  </si>
-  <si>
-    <t>g_IN298-765-IN293-765</t>
-  </si>
-  <si>
-    <t>e_IN300-765</t>
-  </si>
-  <si>
-    <t>e_w409798382-765</t>
-  </si>
-  <si>
-    <t>g_IN300-765-w409798382-765</t>
-  </si>
-  <si>
-    <t>e_IN306-765</t>
-  </si>
-  <si>
-    <t>g_IN306-765-w409798382-765</t>
-  </si>
-  <si>
-    <t>e_IN307-765</t>
-  </si>
-  <si>
-    <t>e_IN302-765</t>
-  </si>
-  <si>
-    <t>g_IN307-765-IN302-765</t>
-  </si>
-  <si>
-    <t>e_IN315-400</t>
-  </si>
-  <si>
-    <t>g_IN315-400-w205942950-400</t>
-  </si>
-  <si>
-    <t>e_IN317-400</t>
-  </si>
-  <si>
-    <t>g_IN317-400-w97392607-400</t>
-  </si>
-  <si>
-    <t>g_IN321-765-IN289-765</t>
-  </si>
-  <si>
-    <t>e_IN323-765</t>
-  </si>
-  <si>
-    <t>g_IN321-765-IN323-765</t>
-  </si>
-  <si>
-    <t>e_IN327-765</t>
-  </si>
-  <si>
-    <t>g_IN323-765-IN327-765</t>
-  </si>
-  <si>
-    <t>e_IN325-400</t>
-  </si>
-  <si>
-    <t>g_IN325-400-w205942950-400</t>
-  </si>
-  <si>
-    <t>e_IN328-765</t>
-  </si>
-  <si>
-    <t>g_IN327-765-IN328-765</t>
-  </si>
-  <si>
-    <t>g_IN328-765-IN327-765</t>
-  </si>
-  <si>
-    <t>e_IN329-765</t>
-  </si>
-  <si>
-    <t>g_IN328-765-IN329-765</t>
-  </si>
-  <si>
-    <t>e_IN343-765</t>
-  </si>
-  <si>
-    <t>g_IN329-765-IN343-765</t>
-  </si>
-  <si>
-    <t>e_IN336-400</t>
-  </si>
-  <si>
-    <t>e_w324064297-400</t>
-  </si>
-  <si>
-    <t>g_IN336-400-w324064297-400</t>
-  </si>
-  <si>
-    <t>e_IN341-400</t>
-  </si>
-  <si>
-    <t>e_w577176545-400</t>
-  </si>
-  <si>
-    <t>g_IN341-400-w577176545-400</t>
-  </si>
-  <si>
-    <t>g_IN343-765-IN329-765</t>
-  </si>
-  <si>
-    <t>e_IN346-765</t>
-  </si>
-  <si>
-    <t>e_IN350-765</t>
-  </si>
-  <si>
-    <t>g_IN346-765-IN350-765</t>
-  </si>
-  <si>
-    <t>g_IN350-765-IN346-765</t>
-  </si>
-  <si>
-    <t>e_IN351-765</t>
-  </si>
-  <si>
-    <t>g_IN350-765-IN351-765</t>
-  </si>
-  <si>
-    <t>e_IN353-400</t>
-  </si>
-  <si>
-    <t>e_IN363-400</t>
-  </si>
-  <si>
-    <t>g_IN353-400-IN363-400</t>
-  </si>
-  <si>
-    <t>e_w209806650-400</t>
-  </si>
-  <si>
-    <t>g_IN363-400-w209806650-400</t>
-  </si>
-  <si>
-    <t>e_IN365-765</t>
-  </si>
-  <si>
-    <t>e_IN367-765</t>
-  </si>
-  <si>
-    <t>g_IN365-765-IN367-765</t>
-  </si>
-  <si>
-    <t>e_IN372-765</t>
-  </si>
-  <si>
-    <t>g_IN367-765-IN372-765</t>
-  </si>
-  <si>
-    <t>e_IN370-765</t>
-  </si>
-  <si>
-    <t>g_IN370-765-IN351-765</t>
-  </si>
-  <si>
-    <t>e_IN376-765</t>
-  </si>
-  <si>
-    <t>g_IN370-765-IN376-765</t>
-  </si>
-  <si>
-    <t>g_IN372-765-IN367-765</t>
-  </si>
-  <si>
-    <t>e_IN373-765</t>
-  </si>
-  <si>
-    <t>g_IN372-765-IN373-765</t>
-  </si>
-  <si>
-    <t>e_w328548895-765</t>
-  </si>
-  <si>
-    <t>g_IN373-765-w328548895-765</t>
-  </si>
-  <si>
-    <t>e_IN382-765</t>
-  </si>
-  <si>
-    <t>g_IN376-765-IN382-765</t>
-  </si>
-  <si>
-    <t>e_IN380-765</t>
-  </si>
-  <si>
-    <t>e_IN381-765</t>
-  </si>
-  <si>
-    <t>g_IN380-765-IN381-765</t>
-  </si>
-  <si>
-    <t>e_IN388-765</t>
-  </si>
-  <si>
-    <t>g_IN380-765-IN388-765</t>
-  </si>
-  <si>
-    <t>e_IN384-765</t>
-  </si>
-  <si>
-    <t>g_IN381-765-IN384-765</t>
-  </si>
-  <si>
-    <t>g_IN382-765-IN376-765</t>
-  </si>
-  <si>
-    <t>e_IN387-765</t>
-  </si>
-  <si>
-    <t>g_IN382-765-IN387-765</t>
-  </si>
-  <si>
-    <t>g_IN384-765-IN381-765</t>
-  </si>
-  <si>
-    <t>e_IN399-765</t>
-  </si>
-  <si>
-    <t>g_IN384-765-IN399-765</t>
-  </si>
-  <si>
-    <t>g_IN387-765-IN382-765</t>
-  </si>
-  <si>
-    <t>g_IN388-765-IN380-765</t>
-  </si>
-  <si>
-    <t>e_IN390-765</t>
-  </si>
-  <si>
-    <t>g_IN388-765-IN390-765</t>
-  </si>
-  <si>
-    <t>e_IN392-765</t>
-  </si>
-  <si>
-    <t>g_IN390-765-IN392-765</t>
-  </si>
-  <si>
-    <t>e_IN391-765</t>
-  </si>
-  <si>
-    <t>g_IN391-765-IN387-765</t>
-  </si>
-  <si>
-    <t>g_IN392-765-IN390-765</t>
-  </si>
-  <si>
-    <t>e_IN393-765</t>
-  </si>
-  <si>
-    <t>g_IN392-765-IN393-765</t>
-  </si>
-  <si>
-    <t>g_IN393-765-IN392-765</t>
-  </si>
-  <si>
-    <t>e_IN395-765</t>
-  </si>
-  <si>
-    <t>g_IN393-765-IN395-765</t>
-  </si>
-  <si>
-    <t>e_IN394-765</t>
-  </si>
-  <si>
-    <t>e_IN401-765</t>
-  </si>
-  <si>
-    <t>g_IN394-765-IN401-765</t>
-  </si>
-  <si>
-    <t>e_IN405-765</t>
-  </si>
-  <si>
-    <t>g_IN395-765-IN405-765</t>
-  </si>
-  <si>
-    <t>e_IN396-765</t>
-  </si>
-  <si>
-    <t>e_IN400-765</t>
-  </si>
-  <si>
-    <t>g_IN396-765-IN400-765</t>
-  </si>
-  <si>
-    <t>e_IN397-765</t>
-  </si>
-  <si>
-    <t>e_IN402-765</t>
-  </si>
-  <si>
-    <t>g_IN397-765-IN402-765</t>
-  </si>
-  <si>
-    <t>g_IN399-765-IN384-765</t>
-  </si>
-  <si>
-    <t>g_IN399-765-IN397-765</t>
-  </si>
-  <si>
-    <t>g_IN400-765-IN391-765</t>
-  </si>
-  <si>
-    <t>g_IN402-765-IN397-765</t>
-  </si>
-  <si>
-    <t>e_IN404-765</t>
-  </si>
-  <si>
-    <t>g_IN402-765-IN404-765</t>
-  </si>
-  <si>
-    <t>e_IN403-765</t>
-  </si>
-  <si>
-    <t>g_IN403-765-IN401-765</t>
-  </si>
-  <si>
-    <t>g_IN403-765-IN405-765</t>
-  </si>
-  <si>
-    <t>g_IN404-765-IN396-765</t>
-  </si>
-  <si>
-    <t>g_IN405-765-IN395-765</t>
-  </si>
-  <si>
-    <t>g_IN405-765-IN403-765</t>
-  </si>
-  <si>
-    <t>e_IN412-765</t>
-  </si>
-  <si>
-    <t>g_IN412-765-IN394-765</t>
-  </si>
-  <si>
-    <t>e_IN413-765</t>
-  </si>
-  <si>
-    <t>e_IN416-765</t>
-  </si>
-  <si>
-    <t>g_IN413-765-IN416-765</t>
-  </si>
-  <si>
-    <t>e_IN439-765</t>
-  </si>
-  <si>
-    <t>g_IN413-765-IN439-765</t>
-  </si>
-  <si>
-    <t>g_IN416-765-IN413-765</t>
-  </si>
-  <si>
-    <t>e_w477691456-765</t>
-  </si>
-  <si>
-    <t>g_IN416-765-w477691456-765</t>
-  </si>
-  <si>
-    <t>e_IN440-400</t>
-  </si>
-  <si>
-    <t>e_w374367235-400</t>
-  </si>
-  <si>
-    <t>g_IN440-400-w374367235-400</t>
-  </si>
-  <si>
-    <t>e_IN457-765</t>
-  </si>
-  <si>
-    <t>g_IN457-765-w607439318-765</t>
-  </si>
-  <si>
-    <t>e_IN473-765</t>
-  </si>
-  <si>
-    <t>e_IN486-765</t>
-  </si>
-  <si>
-    <t>g_IN473-765-IN486-765</t>
-  </si>
-  <si>
-    <t>e_w209826798-765</t>
-  </si>
-  <si>
-    <t>g_IN473-765-w209826798-765</t>
-  </si>
-  <si>
-    <t>e_IN476-765</t>
-  </si>
-  <si>
-    <t>e_w514344408-765</t>
-  </si>
-  <si>
-    <t>g_IN476-765-w514344408-765</t>
-  </si>
-  <si>
-    <t>e_IN488-765</t>
-  </si>
-  <si>
-    <t>g_IN488-765-IN486-765</t>
-  </si>
-  <si>
-    <t>e_IN489-765</t>
-  </si>
-  <si>
-    <t>e_IN490-765</t>
-  </si>
-  <si>
-    <t>g_IN489-765-IN490-765</t>
-  </si>
-  <si>
-    <t>e_IN529-765</t>
-  </si>
-  <si>
-    <t>g_IN489-765-IN529-765</t>
-  </si>
-  <si>
-    <t>g_IN490-765-IN488-765</t>
-  </si>
-  <si>
-    <t>e_w331275940-765</t>
-  </si>
-  <si>
-    <t>g_IN529-765-w331275940-765</t>
-  </si>
-  <si>
-    <t>e_IN532-765</t>
-  </si>
-  <si>
-    <t>e_w248385304-765</t>
-  </si>
-  <si>
-    <t>g_IN532-765-w248385304-765</t>
-  </si>
-  <si>
-    <t>e_w353914865-765</t>
-  </si>
-  <si>
-    <t>g_IN532-765-w353914865-765</t>
-  </si>
-  <si>
-    <t>e_IN537-765</t>
-  </si>
-  <si>
-    <t>e_IN539-765</t>
-  </si>
-  <si>
-    <t>g_IN537-765-IN539-765</t>
-  </si>
-  <si>
-    <t>e_w202980838-765</t>
-  </si>
-  <si>
-    <t>g_IN537-765-w202980838-765</t>
-  </si>
-  <si>
-    <t>e_IN540-765</t>
-  </si>
-  <si>
-    <t>e_w354062412-765</t>
-  </si>
-  <si>
-    <t>g_IN540-765-w354062412-765</t>
-  </si>
-  <si>
-    <t>e_IN541-765</t>
-  </si>
-  <si>
-    <t>e_w319423421-765</t>
-  </si>
-  <si>
-    <t>g_IN541-765-w319423421-765</t>
-  </si>
-  <si>
-    <t>e_IN555-765</t>
-  </si>
-  <si>
-    <t>e_IN578-765</t>
-  </si>
-  <si>
-    <t>g_IN555-765-IN578-765</t>
-  </si>
-  <si>
-    <t>g_IN555-765-w354062412-765</t>
-  </si>
-  <si>
-    <t>e_IN583-765</t>
-  </si>
-  <si>
-    <t>g_IN583-765-IN578-765</t>
-  </si>
-  <si>
-    <t>e_IN586-765</t>
-  </si>
-  <si>
-    <t>g_IN583-765-IN586-765</t>
-  </si>
-  <si>
-    <t>g_IN586-765-IN583-765</t>
-  </si>
-  <si>
-    <t>e_IN599-765</t>
-  </si>
-  <si>
-    <t>g_IN586-765-IN599-765</t>
-  </si>
-  <si>
-    <t>e_IN607-765</t>
-  </si>
-  <si>
-    <t>e_IN609-765</t>
-  </si>
-  <si>
-    <t>g_IN607-765-IN609-765</t>
-  </si>
-  <si>
-    <t>e_IN612-765</t>
-  </si>
-  <si>
-    <t>g_IN607-765-IN612-765</t>
-  </si>
-  <si>
-    <t>g_IN609-765-IN607-765</t>
-  </si>
-  <si>
-    <t>e_IN610-765</t>
-  </si>
-  <si>
-    <t>g_IN609-765-IN610-765</t>
-  </si>
-  <si>
-    <t>g_IN610-765-IN599-765</t>
-  </si>
-  <si>
-    <t>e_IN617-765</t>
-  </si>
-  <si>
-    <t>g_IN612-765-IN617-765</t>
-  </si>
-  <si>
-    <t>g_IN617-765-IN612-765</t>
-  </si>
-  <si>
-    <t>e_IN642-765</t>
-  </si>
-  <si>
-    <t>e_w316463122-765</t>
-  </si>
-  <si>
-    <t>g_IN642-765-w316463122-765</t>
-  </si>
-  <si>
-    <t>e_IN685-765</t>
-  </si>
-  <si>
-    <t>e_IN684-765</t>
-  </si>
-  <si>
-    <t>g_IN685-765-IN684-765</t>
-  </si>
-  <si>
-    <t>e_IN73-765</t>
-  </si>
-  <si>
-    <t>e_w1341291951-765</t>
-  </si>
-  <si>
-    <t>g_IN73-765-w1341291951-765</t>
-  </si>
-  <si>
-    <t>e_IN742-765</t>
-  </si>
-  <si>
-    <t>e_IN748-765</t>
-  </si>
-  <si>
-    <t>g_IN742-765-IN748-765</t>
-  </si>
-  <si>
-    <t>e_w923365745-765</t>
-  </si>
-  <si>
-    <t>g_IN742-765-w923365745-765</t>
-  </si>
-  <si>
-    <t>e_IN749-765</t>
-  </si>
-  <si>
-    <t>g_IN749-765-IN748-765</t>
-  </si>
-  <si>
-    <t>e_IN798-765</t>
-  </si>
-  <si>
-    <t>e_IN801-765</t>
-  </si>
-  <si>
-    <t>g_IN798-765-IN801-765</t>
-  </si>
-  <si>
-    <t>e_IN803-765</t>
-  </si>
-  <si>
-    <t>g_IN801-765-IN803-765</t>
-  </si>
-  <si>
-    <t>e_IN806-765</t>
-  </si>
-  <si>
-    <t>g_IN803-765-IN806-765</t>
-  </si>
-  <si>
-    <t>e_IN807-765</t>
-  </si>
-  <si>
-    <t>e_IN808-765</t>
-  </si>
-  <si>
-    <t>g_IN807-765-IN808-765</t>
-  </si>
-  <si>
-    <t>e_IN85-765</t>
-  </si>
-  <si>
-    <t>g_IN85-765-IN100-765</t>
-  </si>
-  <si>
-    <t>e_w1001700959-765</t>
-  </si>
-  <si>
-    <t>g_w1001700959-765-IN163-765</t>
-  </si>
-  <si>
-    <t>g_w1001700959-765-IN187-765</t>
-  </si>
-  <si>
-    <t>e_IN215-765</t>
-  </si>
-  <si>
-    <t>g_w1001700959-765-IN215-765</t>
-  </si>
-  <si>
-    <t>e_IN375-765</t>
-  </si>
-  <si>
-    <t>g_w100470285-765-IN375-765</t>
-  </si>
-  <si>
-    <t>e_w1238123371-400</t>
-  </si>
-  <si>
-    <t>g_w1012817818-400-w1238123371-400</t>
-  </si>
-  <si>
-    <t>e_w1015325412-400</t>
-  </si>
-  <si>
-    <t>g_w1015325412-400-IN341-400</t>
-  </si>
-  <si>
-    <t>e_w105373531-765</t>
-  </si>
-  <si>
-    <t>e_IN42-765</t>
-  </si>
-  <si>
-    <t>g_w105373531-765-IN42-765</t>
-  </si>
-  <si>
-    <t>e_w1072445901-400</t>
-  </si>
-  <si>
-    <t>g_w1072445901-400-w374367235-400</t>
-  </si>
-  <si>
-    <t>e_w247861059-765</t>
-  </si>
-  <si>
-    <t>g_w1077819664-765-w247861059-765</t>
-  </si>
-  <si>
-    <t>e_w654736039-765</t>
-  </si>
-  <si>
-    <t>g_w1077819664-765-w654736039-765</t>
-  </si>
-  <si>
-    <t>e_w1078426593-765</t>
-  </si>
-  <si>
-    <t>e_w1127651311-765</t>
-  </si>
-  <si>
-    <t>g_w1078426593-765-w1127651311-765</t>
-  </si>
-  <si>
-    <t>e_w1099365556-400</t>
-  </si>
-  <si>
-    <t>e_w1099365579-400</t>
-  </si>
-  <si>
-    <t>g_w1099365556-400-w1099365579-400</t>
-  </si>
-  <si>
-    <t>e_w375941438-400</t>
-  </si>
-  <si>
-    <t>g_w1099365579-400-w375941438-400</t>
-  </si>
-  <si>
-    <t>g_w1127651311-765-w331275940-765</t>
-  </si>
-  <si>
-    <t>e_w688672798-765</t>
-  </si>
-  <si>
-    <t>g_w1127651311-765-w688672798-765</t>
-  </si>
-  <si>
-    <t>e_w631917408-765</t>
-  </si>
-  <si>
-    <t>g_w1143180503-765-w631917408-765</t>
-  </si>
-  <si>
-    <t>g_w1143180503-765-w654736039-765</t>
-  </si>
-  <si>
-    <t>e_w116541259-400</t>
-  </si>
-  <si>
-    <t>g_w116541259-400-IN235-400</t>
-  </si>
-  <si>
-    <t>g_w116541259-400-IN259-400</t>
-  </si>
-  <si>
-    <t>g_w116541259-400-w239498664-400</t>
-  </si>
-  <si>
-    <t>e_w118228036-400</t>
-  </si>
-  <si>
-    <t>g_w118228036-400-IN363-400</t>
-  </si>
-  <si>
-    <t>g_w118228036-400-w205942950-400</t>
-  </si>
-  <si>
-    <t>e_w1206014676-765</t>
-  </si>
-  <si>
-    <t>e_IN809-765</t>
-  </si>
-  <si>
-    <t>g_w1206014676-765-IN809-765</t>
-  </si>
-  <si>
-    <t>e_w1207477934-765</t>
-  </si>
-  <si>
-    <t>e_w801704865-765</t>
-  </si>
-  <si>
-    <t>g_w1207477934-765-w801704865-765</t>
-  </si>
-  <si>
-    <t>g_w1207477934-765-w923365745-765</t>
-  </si>
-  <si>
-    <t>e_IN181-400</t>
-  </si>
-  <si>
-    <t>g_w1238123371-400-IN181-400</t>
-  </si>
-  <si>
-    <t>e_w485873934-400</t>
-  </si>
-  <si>
-    <t>g_w1238123371-400-w485873934-400</t>
-  </si>
-  <si>
-    <t>e_w1246177377-765</t>
-  </si>
-  <si>
-    <t>e_w311933111-765</t>
-  </si>
-  <si>
-    <t>g_w1246177377-765-w311933111-765</t>
-  </si>
-  <si>
-    <t>e_w353914761-765</t>
-  </si>
-  <si>
-    <t>g_w1246177377-765-w353914761-765</t>
-  </si>
-  <si>
-    <t>e_w1265489491-400</t>
-  </si>
-  <si>
-    <t>g_w1265489491-400-IN265-400</t>
-  </si>
-  <si>
-    <t>e_w1265496720-400</t>
-  </si>
-  <si>
-    <t>e_IN145-400</t>
-  </si>
-  <si>
-    <t>g_w1265496720-400-IN145-400</t>
-  </si>
-  <si>
-    <t>e_w375084335-400</t>
-  </si>
-  <si>
-    <t>g_w1265496720-400-w375084335-400</t>
-  </si>
-  <si>
-    <t>g_w131484738-765-IN264-765</t>
-  </si>
-  <si>
-    <t>e_w193216698-765</t>
-  </si>
-  <si>
-    <t>g_w131484738-765-w193216698-765</t>
-  </si>
-  <si>
-    <t>e_w274106872-765</t>
-  </si>
-  <si>
-    <t>g_w131484738-765-w274106872-765</t>
-  </si>
-  <si>
-    <t>e_w1329624553-765</t>
-  </si>
-  <si>
-    <t>e_w781425567-765</t>
-  </si>
-  <si>
-    <t>g_w1329624553-765-w781425567-765</t>
-  </si>
-  <si>
-    <t>g_w1341291951-765-IN73-765</t>
-  </si>
-  <si>
-    <t>e_w1341647644-400</t>
-  </si>
-  <si>
-    <t>g_w1341647644-400-w485873934-400</t>
-  </si>
-  <si>
-    <t>g_w1341647644-400-w526897229-400</t>
-  </si>
-  <si>
-    <t>e_w166692103-400</t>
-  </si>
-  <si>
-    <t>g_w166692103-400-w1012817818-400</t>
-  </si>
-  <si>
-    <t>e_w92360278-400</t>
-  </si>
-  <si>
-    <t>g_w166692103-400-w92360278-400</t>
-  </si>
-  <si>
-    <t>e_w192782338-765</t>
-  </si>
-  <si>
-    <t>g_w192782338-765-w202980838-765</t>
-  </si>
-  <si>
-    <t>g_w193216698-765-w192782338-765</t>
-  </si>
-  <si>
-    <t>e_w195459361-765</t>
-  </si>
-  <si>
-    <t>g_w193216698-765-w195459361-765</t>
-  </si>
-  <si>
-    <t>g_w193216698-765-w319423421-765</t>
-  </si>
-  <si>
-    <t>g_w195459361-765-IN343-765</t>
-  </si>
-  <si>
-    <t>g_w195459361-765-IN346-765</t>
-  </si>
-  <si>
-    <t>g_w195459361-765-IN365-765</t>
-  </si>
-  <si>
-    <t>g_w195459361-765-w193216698-765</t>
-  </si>
-  <si>
-    <t>e_w196933682-765</t>
-  </si>
-  <si>
-    <t>g_w196933682-765-IN375-765</t>
-  </si>
-  <si>
-    <t>g_w196933682-765-w100470285-765</t>
-  </si>
-  <si>
-    <t>e_w201845280-765</t>
-  </si>
-  <si>
-    <t>g_w201845280-765-w192782338-765</t>
-  </si>
-  <si>
-    <t>g_w201845280-765-w311933111-765</t>
-  </si>
-  <si>
-    <t>e_IN535-765</t>
-  </si>
-  <si>
-    <t>g_w202980838-765-IN535-765</t>
-  </si>
-  <si>
-    <t>e_w423166766-765</t>
-  </si>
-  <si>
-    <t>g_w202980838-765-w423166766-765</t>
-  </si>
-  <si>
-    <t>e_w203673991-400</t>
-  </si>
-  <si>
-    <t>g_w203673991-400-w1265496720-400</t>
-  </si>
-  <si>
-    <t>g_w203673991-400-w239498664-400</t>
-  </si>
-  <si>
-    <t>e_w439006823-400</t>
-  </si>
-  <si>
-    <t>g_w203673991-400-w439006823-400</t>
-  </si>
-  <si>
-    <t>e_w610646823-400</t>
-  </si>
-  <si>
-    <t>g_w203673991-400-w610646823-400</t>
-  </si>
-  <si>
-    <t>g_w205942950-400-IN336-400</t>
-  </si>
-  <si>
-    <t>g_w205942950-400-w324064297-400</t>
-  </si>
-  <si>
-    <t>e_w209806624-400</t>
-  </si>
-  <si>
-    <t>g_w209806624-400-IN341-400</t>
-  </si>
-  <si>
-    <t>g_w209806624-400-IN353-400</t>
-  </si>
-  <si>
-    <t>e_w209806624-765</t>
-  </si>
-  <si>
-    <t>g_w209806624-765-IN306-765</t>
-  </si>
-  <si>
-    <t>g_w209826798-765-w193216698-765</t>
-  </si>
-  <si>
-    <t>e_w360424761-765</t>
-  </si>
-  <si>
-    <t>g_w209826798-765-w360424761-765</t>
-  </si>
-  <si>
-    <t>e_w698045832-765</t>
-  </si>
-  <si>
-    <t>g_w209826798-765-w698045832-765</t>
-  </si>
-  <si>
-    <t>g_w239498664-400-IN265-400</t>
-  </si>
-  <si>
-    <t>g_w239498664-400-w203673991-400</t>
-  </si>
-  <si>
-    <t>e_w245128370-765</t>
-  </si>
-  <si>
-    <t>g_w245128370-765-IN749-765</t>
-  </si>
-  <si>
-    <t>e_w315823978-765</t>
-  </si>
-  <si>
-    <t>g_w245128370-765-w315823978-765</t>
-  </si>
-  <si>
-    <t>e_w342204888-765</t>
-  </si>
-  <si>
-    <t>g_w245128370-765-w342204888-765</t>
-  </si>
-  <si>
-    <t>g_w247861059-765-IN85-765</t>
-  </si>
-  <si>
-    <t>g_w247861059-765-w274106872-765</t>
-  </si>
-  <si>
-    <t>e_IN135-765</t>
-  </si>
-  <si>
-    <t>g_w274106872-765-IN135-765</t>
-  </si>
-  <si>
-    <t>e_w293597835-765</t>
-  </si>
-  <si>
-    <t>e_IN659-765</t>
-  </si>
-  <si>
-    <t>g_w293597835-765-IN659-765</t>
-  </si>
-  <si>
-    <t>e_w386018740-765</t>
-  </si>
-  <si>
-    <t>g_w293597835-765-w386018740-765</t>
-  </si>
-  <si>
-    <t>e_w311118424-765</t>
-  </si>
-  <si>
-    <t>g_w311118424-765-IN300-765</t>
-  </si>
-  <si>
-    <t>g_w311118424-765-w274106872-765</t>
-  </si>
-  <si>
-    <t>e_w97392607-765</t>
-  </si>
-  <si>
-    <t>g_w311118424-765-w97392607-765</t>
-  </si>
-  <si>
-    <t>g_w311176519-765-IN142-765</t>
-  </si>
-  <si>
-    <t>g_w311176519-765-w105373531-765</t>
-  </si>
-  <si>
-    <t>g_w311176519-765-w247861059-765</t>
-  </si>
-  <si>
-    <t>e_IN548-765</t>
-  </si>
-  <si>
-    <t>g_w311933111-765-IN548-765</t>
-  </si>
-  <si>
-    <t>e_w311954703-765</t>
-  </si>
-  <si>
-    <t>g_w311933111-765-w311954703-765</t>
-  </si>
-  <si>
-    <t>g_w311954703-765-IN535-765</t>
-  </si>
-  <si>
-    <t>g_w311954703-765-w1246177377-765</t>
-  </si>
-  <si>
-    <t>g_w311954703-765-w353914865-765</t>
-  </si>
-  <si>
-    <t>e_w315477169-765</t>
-  </si>
-  <si>
-    <t>e_w408924420-765</t>
-  </si>
-  <si>
-    <t>g_w315477169-765-w408924420-765</t>
-  </si>
-  <si>
-    <t>e_w315824842-765</t>
-  </si>
-  <si>
-    <t>g_w315823978-765-w315824842-765</t>
-  </si>
-  <si>
-    <t>g_w315823978-765-w801704865-765</t>
-  </si>
-  <si>
-    <t>g_w316463122-765-w201845280-765</t>
-  </si>
-  <si>
-    <t>g_w316463122-765-w293597835-765</t>
-  </si>
-  <si>
-    <t>e_w318050929-765</t>
-  </si>
-  <si>
-    <t>g_w318050929-765-w315477169-765</t>
-  </si>
-  <si>
-    <t>e_w318090288-765</t>
-  </si>
-  <si>
-    <t>g_w318090288-765-w316463122-765</t>
-  </si>
-  <si>
-    <t>g_w318090288-765-w698045832-765</t>
-  </si>
-  <si>
-    <t>g_w319423421-765-IN439-765</t>
-  </si>
-  <si>
-    <t>g_w319423421-765-IN457-765</t>
-  </si>
-  <si>
-    <t>g_w319423421-765-IN476-765</t>
-  </si>
-  <si>
-    <t>g_w319423421-765-w193216698-765</t>
-  </si>
-  <si>
-    <t>g_w319423421-765-w353914865-765</t>
-  </si>
-  <si>
-    <t>e_w323266562-765</t>
-  </si>
-  <si>
-    <t>g_w323266562-765-IN617-765</t>
-  </si>
-  <si>
-    <t>e_w409112085-765</t>
-  </si>
-  <si>
-    <t>g_w323266562-765-w409112085-765</t>
-  </si>
-  <si>
-    <t>e_w324059200-400</t>
-  </si>
-  <si>
-    <t>g_w324059200-400-w97392607-400</t>
-  </si>
-  <si>
-    <t>e_IN320-400</t>
-  </si>
-  <si>
-    <t>g_w324064297-400-IN320-400</t>
-  </si>
-  <si>
-    <t>e_IN339-400</t>
-  </si>
-  <si>
-    <t>g_w324064297-400-IN339-400</t>
-  </si>
-  <si>
-    <t>g_w331275940-765-w318090288-765</t>
-  </si>
-  <si>
-    <t>e_w751947947-765</t>
-  </si>
-  <si>
-    <t>g_w342204888-765-w751947947-765</t>
-  </si>
-  <si>
-    <t>e_w352619220-765</t>
-  </si>
-  <si>
-    <t>e_w311103617-765</t>
-  </si>
-  <si>
-    <t>g_w352619220-765-w311103617-765</t>
-  </si>
-  <si>
-    <t>g_w353914761-765-w353914865-765</t>
-  </si>
-  <si>
-    <t>g_w353914865-765-IN535-765</t>
-  </si>
-  <si>
-    <t>g_w353914865-765-IN540-765</t>
-  </si>
-  <si>
-    <t>g_w353914865-765-IN541-765</t>
-  </si>
-  <si>
-    <t>g_w354062412-765-IN548-765</t>
-  </si>
-  <si>
-    <t>g_w354062412-765-w323266562-765</t>
-  </si>
-  <si>
-    <t>g_w354062412-765-w353914865-765</t>
-  </si>
-  <si>
-    <t>e_w355560316-765</t>
-  </si>
-  <si>
-    <t>e_w386153973-765</t>
-  </si>
-  <si>
-    <t>g_w355560316-765-w386153973-765</t>
-  </si>
-  <si>
-    <t>e_w492377703-765</t>
-  </si>
-  <si>
-    <t>g_w355560316-765-w492377703-765</t>
-  </si>
-  <si>
-    <t>e_w357515226-765</t>
-  </si>
-  <si>
-    <t>g_w357515226-765-IN243-765</t>
-  </si>
-  <si>
-    <t>g_w357515226-765-w409798382-765</t>
-  </si>
-  <si>
-    <t>g_w360424761-765-w319423421-765</t>
-  </si>
-  <si>
-    <t>g_w369866141-765-IN142-765</t>
-  </si>
-  <si>
-    <t>g_w369866141-765-IN230-765</t>
-  </si>
-  <si>
-    <t>e_w311571096-765</t>
-  </si>
-  <si>
-    <t>g_w369866141-765-w311571096-765</t>
-  </si>
-  <si>
-    <t>g_w372701897-765-IN10-765</t>
-  </si>
-  <si>
-    <t>g_w372701897-765-w105373531-765</t>
-  </si>
-  <si>
-    <t>g_w372701897-765-w311176519-765</t>
-  </si>
-  <si>
-    <t>g_w374367235-400-IN260-400</t>
-  </si>
-  <si>
-    <t>e_IN386-400</t>
-  </si>
-  <si>
-    <t>g_w374367235-400-IN386-400</t>
-  </si>
-  <si>
-    <t>g_w374367235-400-w1099365556-400</t>
-  </si>
-  <si>
-    <t>g_w386018740-765-w315823978-765</t>
-  </si>
-  <si>
-    <t>e_w545571850-765</t>
-  </si>
-  <si>
-    <t>g_w386153973-765-w545571850-765</t>
-  </si>
-  <si>
-    <t>e_w408924427-765</t>
-  </si>
-  <si>
-    <t>g_w408924420-765-w408924427-765</t>
-  </si>
-  <si>
-    <t>e_w409158116-765</t>
-  </si>
-  <si>
-    <t>g_w409112085-765-w409158116-765</t>
-  </si>
-  <si>
-    <t>g_w409158116-765-IN685-765</t>
-  </si>
-  <si>
-    <t>g_w409798382-765-w477691456-765</t>
-  </si>
-  <si>
-    <t>g_w409798382-765-w97392607-765</t>
-  </si>
-  <si>
-    <t>e_w417569420-765</t>
-  </si>
-  <si>
-    <t>e_IN267-765</t>
-  </si>
-  <si>
-    <t>g_w417569420-765-IN267-765</t>
-  </si>
-  <si>
-    <t>g_w417569420-765-IN73-765</t>
-  </si>
-  <si>
-    <t>g_w417569420-765-w781425567-765</t>
-  </si>
-  <si>
-    <t>e_w420797421-765</t>
-  </si>
-  <si>
-    <t>g_w420797421-765-IN135-765</t>
-  </si>
-  <si>
-    <t>g_w420797421-765-w105373531-765</t>
-  </si>
-  <si>
-    <t>g_w420797421-765-w1329624553-765</t>
-  </si>
-  <si>
-    <t>g_w420797421-765-w417569420-765</t>
-  </si>
-  <si>
-    <t>e_w425101516-765</t>
-  </si>
-  <si>
-    <t>g_w420797421-765-w425101516-765</t>
-  </si>
-  <si>
-    <t>e_w422204218-765</t>
-  </si>
-  <si>
-    <t>e_IN312-765</t>
-  </si>
-  <si>
-    <t>g_w422204218-765-IN312-765</t>
-  </si>
-  <si>
-    <t>g_w423702239-765-IN295-765</t>
-  </si>
-  <si>
-    <t>g_w425101516-765-IN171-765</t>
-  </si>
-  <si>
-    <t>g_w425101516-765-IN267-765</t>
-  </si>
-  <si>
-    <t>e_w425401901-765</t>
-  </si>
-  <si>
-    <t>g_w425401901-765-w386153973-765</t>
-  </si>
-  <si>
-    <t>e_w429459345-765</t>
-  </si>
-  <si>
-    <t>g_w429459345-765-w492377703-765</t>
-  </si>
-  <si>
-    <t>g_w439006823-400-w374367235-400</t>
-  </si>
-  <si>
-    <t>g_w439006823-400-w375941438-400</t>
-  </si>
-  <si>
-    <t>e_w453513742-765</t>
-  </si>
-  <si>
-    <t>g_w453513742-765-IN642-765</t>
-  </si>
-  <si>
-    <t>g_w453513742-765-IN659-765</t>
-  </si>
-  <si>
-    <t>e_w465787206-400</t>
-  </si>
-  <si>
-    <t>g_w465787206-400-w239498664-400</t>
-  </si>
-  <si>
-    <t>e_w466424134-765</t>
-  </si>
-  <si>
-    <t>g_w466424134-765-w201845280-765</t>
-  </si>
-  <si>
-    <t>e_w473902678-765</t>
-  </si>
-  <si>
-    <t>g_w473902678-765-IN642-765</t>
-  </si>
-  <si>
-    <t>g_w477691456-765-IN412-765</t>
-  </si>
-  <si>
-    <t>e_w196563905-765</t>
-  </si>
-  <si>
-    <t>g_w477691456-765-w196563905-765</t>
-  </si>
-  <si>
-    <t>g_w477691456-765-w328548895-765</t>
-  </si>
-  <si>
-    <t>g_w485873934-400-w92360278-400</t>
-  </si>
-  <si>
-    <t>e_w485873968-400</t>
-  </si>
-  <si>
-    <t>g_w485873968-400-w205942950-400</t>
-  </si>
-  <si>
-    <t>e_w506461670-765</t>
-  </si>
-  <si>
-    <t>g_w506461670-765-IN539-765</t>
-  </si>
-  <si>
-    <t>g_w506461670-765-w311933111-765</t>
-  </si>
-  <si>
-    <t>e_w840600239-765</t>
-  </si>
-  <si>
-    <t>g_w506461670-765-w840600239-765</t>
-  </si>
-  <si>
-    <t>e_w50885643-400</t>
-  </si>
-  <si>
-    <t>g_w50885643-400-IN285-400</t>
-  </si>
-  <si>
-    <t>e_w92994753-400</t>
-  </si>
-  <si>
-    <t>g_w50885643-400-w92994753-400</t>
-  </si>
-  <si>
-    <t>e_w96821783-400</t>
-  </si>
-  <si>
-    <t>g_w50885643-400-w96821783-400</t>
-  </si>
-  <si>
-    <t>e_w50885643-765</t>
-  </si>
-  <si>
-    <t>g_w50885643-765-IN300-765</t>
-  </si>
-  <si>
-    <t>g_w50885643-765-w209806624-765</t>
-  </si>
-  <si>
-    <t>g_w50885643-765-w311103617-765</t>
-  </si>
-  <si>
-    <t>e_w521570801-765</t>
-  </si>
-  <si>
-    <t>g_w521570801-765-w354062412-765</t>
-  </si>
-  <si>
-    <t>e_IN155-400</t>
-  </si>
-  <si>
-    <t>g_w526897229-400-IN155-400</t>
-  </si>
-  <si>
-    <t>e_w551402699-765</t>
-  </si>
-  <si>
-    <t>g_w551402699-765-IN135-765</t>
-  </si>
-  <si>
-    <t>g_w551402699-765-IN136-765</t>
-  </si>
-  <si>
-    <t>e_IN140-765</t>
-  </si>
-  <si>
-    <t>g_w551402699-765-IN140-765</t>
-  </si>
-  <si>
-    <t>g_w551402699-765-w607439318-765</t>
-  </si>
-  <si>
-    <t>e_w1044735753-400</t>
-  </si>
-  <si>
-    <t>g_w577176545-400-w1044735753-400</t>
-  </si>
-  <si>
-    <t>e_w608461884-765</t>
-  </si>
-  <si>
-    <t>g_w608461884-765-w293597835-765</t>
-  </si>
-  <si>
-    <t>g_w631917408-765-w369866141-765</t>
-  </si>
-  <si>
-    <t>g_w654736039-765-w372701897-765</t>
-  </si>
-  <si>
-    <t>e_w655683221-765</t>
-  </si>
-  <si>
-    <t>g_w655683221-765-w631917408-765</t>
-  </si>
-  <si>
-    <t>g_w655683221-765-w688672798-765</t>
-  </si>
-  <si>
-    <t>g_w686891085-765-w654736039-765</t>
-  </si>
-  <si>
-    <t>e_w688672711-765</t>
-  </si>
-  <si>
-    <t>g_w688672711-765-w1078426593-765</t>
-  </si>
-  <si>
-    <t>e_w1336628403-765</t>
-  </si>
-  <si>
-    <t>g_w688672711-765-w1336628403-765</t>
-  </si>
-  <si>
-    <t>g_w688672711-765-w688672798-765</t>
-  </si>
-  <si>
-    <t>e_w759521252-765</t>
-  </si>
-  <si>
-    <t>g_w759521252-765-w248385304-765</t>
-  </si>
-  <si>
-    <t>e_w793144832-765</t>
-  </si>
-  <si>
-    <t>g_w759521252-765-w793144832-765</t>
-  </si>
-  <si>
-    <t>e_IN160-765</t>
-  </si>
-  <si>
-    <t>g_w781425567-765-IN160-765</t>
-  </si>
-  <si>
-    <t>e_IN167-765</t>
-  </si>
-  <si>
-    <t>g_w781425567-765-IN167-765</t>
-  </si>
-  <si>
-    <t>g_w781425567-765-w422204218-765</t>
-  </si>
-  <si>
-    <t>g_w801704865-765-w466424134-765</t>
-  </si>
-  <si>
-    <t>g_w840600239-765-w1207477934-765</t>
-  </si>
-  <si>
-    <t>g_w840600239-765-w514344408-765</t>
-  </si>
-  <si>
-    <t>g_w840600239-765-w608461884-765</t>
-  </si>
-  <si>
-    <t>e_w910151268-765</t>
-  </si>
-  <si>
-    <t>e_w1074489047-765</t>
-  </si>
-  <si>
-    <t>g_w910151268-765-w1074489047-765</t>
-  </si>
-  <si>
-    <t>g_w910151268-765-w751947947-765</t>
-  </si>
-  <si>
-    <t>g_w923365745-765-IN684-765</t>
-  </si>
-  <si>
-    <t>e_w923418232-400</t>
-  </si>
-  <si>
-    <t>g_w923418232-400-w97392607-400</t>
-  </si>
-  <si>
-    <t>e_IN179-400</t>
-  </si>
-  <si>
-    <t>g_w92360278-400-IN179-400</t>
-  </si>
-  <si>
-    <t>g_w92360278-400-w96821783-400</t>
-  </si>
-  <si>
-    <t>g_w92994753-400-IN285-400</t>
-  </si>
-  <si>
-    <t>g_w92994753-400-IN286-400</t>
-  </si>
-  <si>
-    <t>g_w92994753-400-w1044735753-400</t>
-  </si>
-  <si>
-    <t>g_w92994753-400-w1341647644-400</t>
-  </si>
-  <si>
-    <t>g_w93160503-400-IN320-400</t>
-  </si>
-  <si>
-    <t>g_w93160503-400-IN339-400</t>
-  </si>
-  <si>
-    <t>g_w93160503-400-w116541259-400</t>
-  </si>
-  <si>
-    <t>g_w93160503-400-w92360278-400</t>
-  </si>
-  <si>
-    <t>g_w94199110-400-IN286-400</t>
-  </si>
-  <si>
-    <t>g_w96821783-400-IN325-400</t>
-  </si>
-  <si>
-    <t>e_w149822703-400</t>
-  </si>
-  <si>
-    <t>g_w96821783-400-w149822703-400</t>
-  </si>
-  <si>
-    <t>g_w96821783-400-w209806650-400</t>
-  </si>
-  <si>
-    <t>e_w409798382-400</t>
-  </si>
-  <si>
-    <t>g_w96821783-400-w409798382-400</t>
-  </si>
-  <si>
-    <t>g_w96821783-400-w485873968-400</t>
-  </si>
-  <si>
-    <t>g_w96821783-400-w93160503-400</t>
-  </si>
-  <si>
-    <t>g_w97392607-400-IN317-400</t>
-  </si>
-  <si>
-    <t>g_w97392607-400-w96821783-400</t>
-  </si>
-  <si>
-    <t>g_w97392607-765-w209806624-765</t>
+    <t>e_IN100-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN101-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN100-765_IND-IN101-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN104-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN101-765_IND-IN104-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN105-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN105-765_IND-IN104-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN136-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN105-765_IND-IN136-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN107-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN94-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN107-765_IND-IN94-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN108-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1077819664-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN108-765_IND-w1077819664-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN116-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1415199647-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN116-765_IND-w1415199647-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN120-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN120-765_IND-w1415199647-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN123-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN121-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN123-765_IND-IN121-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN125-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN123-765_IND-IN125-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN126-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN128-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN126-765_IND-IN128-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN243-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN136-765_IND-IN243-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN137-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN146-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN137-765_IND-IN146-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN139-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN138-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN139-765_IND-IN138-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN142-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN142-765_IND-w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>e_w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN142-765_IND-w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN148-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN148-765_IND-w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN159-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN164-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN159-765_IND-IN164-765_IND</t>
+  </si>
+  <si>
+    <t>e_w686891085-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN159-765_IND-w686891085-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN161-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN161-765_IND-w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN163-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN163-765_IND-IN161-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN164-765_IND-IN159-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN187-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN164-765_IND-IN187-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN171-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN174-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN171-765_IND-IN174-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN177-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN176-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN177-400_IND-IN176-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN178-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN175-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN178-765_IND-IN175-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN190-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN183-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN190-765_IND-IN183-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN191-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN191-765_IND-w1143180503-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN196-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN196-765_IND-IN174-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN197-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN194-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN197-765_IND-IN194-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN200-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN200-765_IND-IN196-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN201-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN198-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN201-765_IND-IN198-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN202-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN180-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN202-765_IND-IN180-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN205-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN203-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN205-765_IND-IN203-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN206-765_IND</t>
+  </si>
+  <si>
+    <t>e_w100470285-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN206-765_IND-w100470285-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN218-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN199-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN218-765_IND-IN199-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN222-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN217-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN222-765_IND-IN217-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN225-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN225-765_IND-IN200-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN229-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN229-765_IND-IN225-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN239-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN229-765_IND-IN239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN230-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN233-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN230-765_IND-IN233-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN230-765_IND-w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN244-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN233-765_IND-IN244-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN235-400_IND</t>
+  </si>
+  <si>
+    <t>e_w239498664-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN235-400_IND-w239498664-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN239-765_IND-IN229-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN240-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN240-765_IND-IN239-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN244-765_IND-IN233-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN247-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN244-765_IND-IN247-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN246-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN250-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN246-765_IND-IN250-765_IND</t>
+  </si>
+  <si>
+    <t>e_w131484738-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN246-765_IND-w131484738-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN249-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN247-765_IND-IN249-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN249-765_IND-IN247-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN250-765_IND-IN246-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN250-765_IND-IN249-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN253-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN232-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN253-765_IND-IN232-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN254-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN254-765_IND-IN253-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN255-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN257-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN255-765_IND-IN257-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN259-400_IND</t>
+  </si>
+  <si>
+    <t>e_w526897229-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN259-400_IND-w526897229-400_IND</t>
+  </si>
+  <si>
+    <t>e_w93160503-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN259-400_IND-w93160503-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN263-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN262-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN263-400_IND-IN262-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN264-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN270-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN264-765_IND-IN270-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN265-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN260-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN265-400_IND-IN260-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN268-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN258-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN268-765_IND-IN258-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN270-765_IND-IN264-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN272-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN270-765_IND-IN272-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN276-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN272-765_IND-IN276-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN275-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN269-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN275-765_IND-IN269-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN276-765_IND-IN272-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN277-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN276-765_IND-IN277-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN278-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN278-765_IND-IN277-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN279-765_IND</t>
+  </si>
+  <si>
+    <t>e_w607439318-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN279-765_IND-w607439318-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN280-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN280-765_IND-IN279-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN282-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN282-765_IND-IN240-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN284-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN282-765_IND-IN284-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN292-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN284-765_IND-IN292-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN285-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN287-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN285-400_IND-IN287-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN286-400_IND</t>
+  </si>
+  <si>
+    <t>e_w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN286-400_IND-w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1012817818-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN287-400_IND-w1012817818-400_IND</t>
+  </si>
+  <si>
+    <t>e_w94199110-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN287-400_IND-w94199110-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN288-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN288-765_IND-IN278-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN289-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN289-765_IND-IN288-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN321-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN289-765_IND-IN321-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN290-400_IND</t>
+  </si>
+  <si>
+    <t>e_w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN290-400_IND-w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN295-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN292-765_IND-IN295-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN293-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN283-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN293-765_IND-IN283-765_IND</t>
+  </si>
+  <si>
+    <t>e_w423702239-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN295-765_IND-w423702239-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN298-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN298-765_IND-IN293-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN300-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409798382-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN300-765_IND-w409798382-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN306-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN306-765_IND-w409798382-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN307-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN302-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN307-765_IND-IN302-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN315-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN315-400_IND-w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN317-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN317-400_IND-w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN321-765_IND-IN289-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN323-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN321-765_IND-IN323-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN327-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN323-765_IND-IN327-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN325-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN325-400_IND-w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN328-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN327-765_IND-IN328-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN328-765_IND-IN327-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN329-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN328-765_IND-IN329-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN343-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN329-765_IND-IN343-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN336-400_IND</t>
+  </si>
+  <si>
+    <t>e_w324064297-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN336-400_IND-w324064297-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN341-400_IND</t>
+  </si>
+  <si>
+    <t>e_w577176545-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN341-400_IND-w577176545-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN343-765_IND-IN329-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN346-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN350-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN346-765_IND-IN350-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN350-765_IND-IN346-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN351-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN350-765_IND-IN351-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN353-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN363-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN353-400_IND-IN363-400_IND</t>
+  </si>
+  <si>
+    <t>e_w209806650-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN363-400_IND-w209806650-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN365-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN367-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN365-765_IND-IN367-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN372-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN367-765_IND-IN372-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN370-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN370-765_IND-IN351-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN376-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN370-765_IND-IN376-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN372-765_IND-IN367-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN373-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN372-765_IND-IN373-765_IND</t>
+  </si>
+  <si>
+    <t>e_w328548895-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN373-765_IND-w328548895-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN382-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN376-765_IND-IN382-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN380-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN381-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN380-765_IND-IN381-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN388-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN380-765_IND-IN388-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN384-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN381-765_IND-IN384-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN382-765_IND-IN376-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN387-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN382-765_IND-IN387-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN384-765_IND-IN381-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN399-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN384-765_IND-IN399-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN387-765_IND-IN382-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN388-765_IND-IN380-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN390-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN388-765_IND-IN390-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN392-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN390-765_IND-IN392-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN391-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN391-765_IND-IN387-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN392-765_IND-IN390-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN393-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN392-765_IND-IN393-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN393-765_IND-IN392-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN395-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN393-765_IND-IN395-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN394-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN401-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN394-765_IND-IN401-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN405-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN395-765_IND-IN405-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN396-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN400-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN396-765_IND-IN400-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN397-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN402-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN397-765_IND-IN402-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN399-765_IND-IN384-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN399-765_IND-IN397-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN400-765_IND-IN391-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN402-765_IND-IN397-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN404-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN402-765_IND-IN404-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN403-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN403-765_IND-IN401-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN403-765_IND-IN405-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN404-765_IND-IN396-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN405-765_IND-IN395-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN405-765_IND-IN403-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN412-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN412-765_IND-IN394-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN413-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN416-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN413-765_IND-IN416-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN439-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN413-765_IND-IN439-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN416-765_IND-IN413-765_IND</t>
+  </si>
+  <si>
+    <t>e_w477691456-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN416-765_IND-w477691456-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN440-400_IND</t>
+  </si>
+  <si>
+    <t>e_w374367235-400_IND</t>
+  </si>
+  <si>
+    <t>g_IN440-400_IND-w374367235-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN457-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN457-765_IND-w607439318-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN473-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN486-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN473-765_IND-IN486-765_IND</t>
+  </si>
+  <si>
+    <t>e_w209826798-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN473-765_IND-w209826798-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN476-765_IND</t>
+  </si>
+  <si>
+    <t>e_w514344408-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN476-765_IND-w514344408-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN488-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN488-765_IND-IN486-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN489-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN490-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN489-765_IND-IN490-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN529-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN489-765_IND-IN529-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN490-765_IND-IN488-765_IND</t>
+  </si>
+  <si>
+    <t>e_w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN529-765_IND-w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN532-765_IND</t>
+  </si>
+  <si>
+    <t>e_w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN532-765_IND-w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>e_w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN532-765_IND-w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN537-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN539-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN537-765_IND-IN539-765_IND</t>
+  </si>
+  <si>
+    <t>e_w202980838-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN537-765_IND-w202980838-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN540-765_IND</t>
+  </si>
+  <si>
+    <t>e_w354062412-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN540-765_IND-w354062412-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN541-765_IND</t>
+  </si>
+  <si>
+    <t>e_w319423421-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN541-765_IND-w319423421-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN555-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN578-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN555-765_IND-IN578-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN555-765_IND-w354062412-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN583-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN583-765_IND-IN578-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN586-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN583-765_IND-IN586-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN586-765_IND-IN583-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN599-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN586-765_IND-IN599-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN607-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN609-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN607-765_IND-IN609-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN612-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN607-765_IND-IN612-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN609-765_IND-IN607-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN610-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN609-765_IND-IN610-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN610-765_IND-IN599-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN617-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN612-765_IND-IN617-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN617-765_IND-IN612-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN642-765_IND</t>
+  </si>
+  <si>
+    <t>e_w316463122-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN642-765_IND-w316463122-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN685-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN684-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN685-765_IND-IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN73-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN73-765_IND-w1341291951-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN742-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN748-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN742-765_IND-IN748-765_IND</t>
+  </si>
+  <si>
+    <t>e_w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN742-765_IND-w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN749-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN749-765_IND-IN748-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN798-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN801-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN798-765_IND-IN801-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN803-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN801-765_IND-IN803-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN806-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN803-765_IND-IN806-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN807-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN808-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN807-765_IND-IN808-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN85-765_IND</t>
+  </si>
+  <si>
+    <t>g_IN85-765_IND-IN100-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1001700959-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1001700959-765_IND-IN163-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1001700959-765_IND-IN187-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN215-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1001700959-765_IND-IN215-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN375-765_IND</t>
+  </si>
+  <si>
+    <t>g_w100470285-765_IND-IN375-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1238123371-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1012817818-400_IND-w1238123371-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1015325412-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1015325412-400_IND-IN341-400_IND</t>
+  </si>
+  <si>
+    <t>e_w105373531-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN42-765_IND</t>
+  </si>
+  <si>
+    <t>g_w105373531-765_IND-IN42-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1072445901-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1072445901-400_IND-w374367235-400_IND</t>
+  </si>
+  <si>
+    <t>e_w247861059-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1077819664-765_IND-w247861059-765_IND</t>
+  </si>
+  <si>
+    <t>e_w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1077819664-765_IND-w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1078426593-765_IND-w1127651311-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365556-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1099365556-400_IND-w1099365579-400_IND</t>
+  </si>
+  <si>
+    <t>e_w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1099365579-400_IND-w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1127651311-765_IND-w331275940-765_IND</t>
+  </si>
+  <si>
+    <t>e_w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1127651311-765_IND-w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1143180503-765_IND-w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1143180503-765_IND-w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w116541259-400_IND</t>
+  </si>
+  <si>
+    <t>g_w116541259-400_IND-IN235-400_IND</t>
+  </si>
+  <si>
+    <t>g_w116541259-400_IND-IN259-400_IND</t>
+  </si>
+  <si>
+    <t>g_w116541259-400_IND-w239498664-400_IND</t>
+  </si>
+  <si>
+    <t>e_w118228036-400_IND</t>
+  </si>
+  <si>
+    <t>g_w118228036-400_IND-IN363-400_IND</t>
+  </si>
+  <si>
+    <t>g_w118228036-400_IND-w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1206014676-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN809-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1206014676-765_IND-IN809-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>e_w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1207477934-765_IND-w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1207477934-765_IND-w923365745-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN181-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1238123371-400_IND-IN181-400_IND</t>
+  </si>
+  <si>
+    <t>e_w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1238123371-400_IND-w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1246177377-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311933111-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1246177377-765_IND-w311933111-765_IND</t>
+  </si>
+  <si>
+    <t>e_w353914761-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1246177377-765_IND-w353914761-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1265489491-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1265489491-400_IND-IN265-400_IND</t>
+  </si>
+  <si>
+    <t>e_w1265496720-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN145-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1265496720-400_IND-IN145-400_IND</t>
+  </si>
+  <si>
+    <t>e_w375084335-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1265496720-400_IND-w375084335-400_IND</t>
+  </si>
+  <si>
+    <t>g_w131484738-765_IND-IN264-765_IND</t>
+  </si>
+  <si>
+    <t>e_w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>g_w131484738-765_IND-w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>e_w274106872-765_IND</t>
+  </si>
+  <si>
+    <t>g_w131484738-765_IND-w274106872-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1329624553-765_IND</t>
+  </si>
+  <si>
+    <t>e_w781425567-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1329624553-765_IND-w781425567-765_IND</t>
+  </si>
+  <si>
+    <t>g_w1341291951-765_IND-IN73-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1341647644-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1341647644-400_IND-w485873934-400_IND</t>
+  </si>
+  <si>
+    <t>g_w1341647644-400_IND-w526897229-400_IND</t>
+  </si>
+  <si>
+    <t>e_w166692103-400_IND</t>
+  </si>
+  <si>
+    <t>g_w166692103-400_IND-w1012817818-400_IND</t>
+  </si>
+  <si>
+    <t>e_w92360278-400_IND</t>
+  </si>
+  <si>
+    <t>g_w166692103-400_IND-w92360278-400_IND</t>
+  </si>
+  <si>
+    <t>e_w192782338-765_IND</t>
+  </si>
+  <si>
+    <t>g_w192782338-765_IND-w202980838-765_IND</t>
+  </si>
+  <si>
+    <t>g_w193216698-765_IND-w192782338-765_IND</t>
+  </si>
+  <si>
+    <t>e_w195459361-765_IND</t>
+  </si>
+  <si>
+    <t>g_w193216698-765_IND-w195459361-765_IND</t>
+  </si>
+  <si>
+    <t>g_w193216698-765_IND-w319423421-765_IND</t>
+  </si>
+  <si>
+    <t>g_w195459361-765_IND-IN343-765_IND</t>
+  </si>
+  <si>
+    <t>g_w195459361-765_IND-IN346-765_IND</t>
+  </si>
+  <si>
+    <t>g_w195459361-765_IND-IN365-765_IND</t>
+  </si>
+  <si>
+    <t>g_w195459361-765_IND-w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>e_w196933682-765_IND</t>
+  </si>
+  <si>
+    <t>g_w196933682-765_IND-IN375-765_IND</t>
+  </si>
+  <si>
+    <t>g_w196933682-765_IND-w100470285-765_IND</t>
+  </si>
+  <si>
+    <t>e_w201845280-765_IND</t>
+  </si>
+  <si>
+    <t>g_w201845280-765_IND-w192782338-765_IND</t>
+  </si>
+  <si>
+    <t>g_w201845280-765_IND-w311933111-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN535-765_IND</t>
+  </si>
+  <si>
+    <t>g_w202980838-765_IND-IN535-765_IND</t>
+  </si>
+  <si>
+    <t>e_w423166766-765_IND</t>
+  </si>
+  <si>
+    <t>g_w202980838-765_IND-w423166766-765_IND</t>
+  </si>
+  <si>
+    <t>e_w203673991-400_IND</t>
+  </si>
+  <si>
+    <t>g_w203673991-400_IND-w1265496720-400_IND</t>
+  </si>
+  <si>
+    <t>g_w203673991-400_IND-w239498664-400_IND</t>
+  </si>
+  <si>
+    <t>e_w439006823-400_IND</t>
+  </si>
+  <si>
+    <t>g_w203673991-400_IND-w439006823-400_IND</t>
+  </si>
+  <si>
+    <t>e_w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>g_w203673991-400_IND-w610646823-400_IND</t>
+  </si>
+  <si>
+    <t>g_w205942950-400_IND-IN336-400_IND</t>
+  </si>
+  <si>
+    <t>g_w205942950-400_IND-w324064297-400_IND</t>
+  </si>
+  <si>
+    <t>e_w209806624-400_IND</t>
+  </si>
+  <si>
+    <t>g_w209806624-400_IND-IN341-400_IND</t>
+  </si>
+  <si>
+    <t>g_w209806624-400_IND-IN353-400_IND</t>
+  </si>
+  <si>
+    <t>e_w209806624-765_IND</t>
+  </si>
+  <si>
+    <t>g_w209806624-765_IND-IN306-765_IND</t>
+  </si>
+  <si>
+    <t>g_w209826798-765_IND-w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>e_w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>g_w209826798-765_IND-w360424761-765_IND</t>
+  </si>
+  <si>
+    <t>e_w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>g_w209826798-765_IND-w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>g_w239498664-400_IND-IN265-400_IND</t>
+  </si>
+  <si>
+    <t>g_w239498664-400_IND-w203673991-400_IND</t>
+  </si>
+  <si>
+    <t>e_w245128370-765_IND</t>
+  </si>
+  <si>
+    <t>g_w245128370-765_IND-IN749-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>g_w245128370-765_IND-w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>e_w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>g_w245128370-765_IND-w342204888-765_IND</t>
+  </si>
+  <si>
+    <t>g_w247861059-765_IND-IN85-765_IND</t>
+  </si>
+  <si>
+    <t>g_w247861059-765_IND-w274106872-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN135-765_IND</t>
+  </si>
+  <si>
+    <t>g_w274106872-765_IND-IN135-765_IND</t>
+  </si>
+  <si>
+    <t>e_w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN659-765_IND</t>
+  </si>
+  <si>
+    <t>g_w293597835-765_IND-IN659-765_IND</t>
+  </si>
+  <si>
+    <t>e_w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>g_w293597835-765_IND-w386018740-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311118424-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311118424-765_IND-IN300-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311118424-765_IND-w274106872-765_IND</t>
+  </si>
+  <si>
+    <t>e_w97392607-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311118424-765_IND-w97392607-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311176519-765_IND-IN142-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311176519-765_IND-w105373531-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311176519-765_IND-w247861059-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN548-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311933111-765_IND-IN548-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311933111-765_IND-w311954703-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311954703-765_IND-IN535-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311954703-765_IND-w1246177377-765_IND</t>
+  </si>
+  <si>
+    <t>g_w311954703-765_IND-w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315477169-765_IND</t>
+  </si>
+  <si>
+    <t>e_w408924420-765_IND</t>
+  </si>
+  <si>
+    <t>g_w315477169-765_IND-w408924420-765_IND</t>
+  </si>
+  <si>
+    <t>e_w315824842-765_IND</t>
+  </si>
+  <si>
+    <t>g_w315823978-765_IND-w315824842-765_IND</t>
+  </si>
+  <si>
+    <t>g_w315823978-765_IND-w801704865-765_IND</t>
+  </si>
+  <si>
+    <t>g_w316463122-765_IND-w201845280-765_IND</t>
+  </si>
+  <si>
+    <t>g_w316463122-765_IND-w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>e_w318050929-765_IND</t>
+  </si>
+  <si>
+    <t>g_w318050929-765_IND-w315477169-765_IND</t>
+  </si>
+  <si>
+    <t>e_w318090288-765_IND</t>
+  </si>
+  <si>
+    <t>g_w318090288-765_IND-w316463122-765_IND</t>
+  </si>
+  <si>
+    <t>g_w318090288-765_IND-w698045832-765_IND</t>
+  </si>
+  <si>
+    <t>g_w319423421-765_IND-IN439-765_IND</t>
+  </si>
+  <si>
+    <t>g_w319423421-765_IND-IN457-765_IND</t>
+  </si>
+  <si>
+    <t>g_w319423421-765_IND-IN476-765_IND</t>
+  </si>
+  <si>
+    <t>g_w319423421-765_IND-w193216698-765_IND</t>
+  </si>
+  <si>
+    <t>g_w319423421-765_IND-w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>g_w323266562-765_IND-IN617-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>g_w323266562-765_IND-w409112085-765_IND</t>
+  </si>
+  <si>
+    <t>e_w324059200-400_IND</t>
+  </si>
+  <si>
+    <t>g_w324059200-400_IND-w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN320-400_IND</t>
+  </si>
+  <si>
+    <t>g_w324064297-400_IND-IN320-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN339-400_IND</t>
+  </si>
+  <si>
+    <t>g_w324064297-400_IND-IN339-400_IND</t>
+  </si>
+  <si>
+    <t>g_w331275940-765_IND-w318090288-765_IND</t>
+  </si>
+  <si>
+    <t>e_w751947947-765_IND</t>
+  </si>
+  <si>
+    <t>g_w342204888-765_IND-w751947947-765_IND</t>
+  </si>
+  <si>
+    <t>e_w352619220-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>g_w352619220-765_IND-w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>g_w353914761-765_IND-w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>g_w353914865-765_IND-IN535-765_IND</t>
+  </si>
+  <si>
+    <t>g_w353914865-765_IND-IN540-765_IND</t>
+  </si>
+  <si>
+    <t>g_w353914865-765_IND-IN541-765_IND</t>
+  </si>
+  <si>
+    <t>g_w354062412-765_IND-IN548-765_IND</t>
+  </si>
+  <si>
+    <t>g_w354062412-765_IND-w323266562-765_IND</t>
+  </si>
+  <si>
+    <t>g_w354062412-765_IND-w353914865-765_IND</t>
+  </si>
+  <si>
+    <t>e_w355560316-765_IND</t>
+  </si>
+  <si>
+    <t>e_w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>g_w355560316-765_IND-w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>e_w492377703-765_IND</t>
+  </si>
+  <si>
+    <t>g_w355560316-765_IND-w492377703-765_IND</t>
+  </si>
+  <si>
+    <t>e_w357515226-765_IND</t>
+  </si>
+  <si>
+    <t>g_w357515226-765_IND-IN243-765_IND</t>
+  </si>
+  <si>
+    <t>g_w357515226-765_IND-w409798382-765_IND</t>
+  </si>
+  <si>
+    <t>g_w360424761-765_IND-w319423421-765_IND</t>
+  </si>
+  <si>
+    <t>g_w369866141-765_IND-IN142-765_IND</t>
+  </si>
+  <si>
+    <t>g_w369866141-765_IND-IN230-765_IND</t>
+  </si>
+  <si>
+    <t>e_w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>g_w369866141-765_IND-w311571096-765_IND</t>
+  </si>
+  <si>
+    <t>g_w372701897-765_IND-IN10-765_IND</t>
+  </si>
+  <si>
+    <t>g_w372701897-765_IND-w105373531-765_IND</t>
+  </si>
+  <si>
+    <t>g_w372701897-765_IND-w311176519-765_IND</t>
+  </si>
+  <si>
+    <t>g_w374367235-400_IND-IN260-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN386-400_IND</t>
+  </si>
+  <si>
+    <t>g_w374367235-400_IND-IN386-400_IND</t>
+  </si>
+  <si>
+    <t>g_w374367235-400_IND-w1099365556-400_IND</t>
+  </si>
+  <si>
+    <t>g_w386018740-765_IND-w315823978-765_IND</t>
+  </si>
+  <si>
+    <t>e_w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>g_w386153973-765_IND-w545571850-765_IND</t>
+  </si>
+  <si>
+    <t>e_w408924427-765_IND</t>
+  </si>
+  <si>
+    <t>g_w408924420-765_IND-w408924427-765_IND</t>
+  </si>
+  <si>
+    <t>e_w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>g_w409112085-765_IND-w409158116-765_IND</t>
+  </si>
+  <si>
+    <t>g_w409158116-765_IND-IN685-765_IND</t>
+  </si>
+  <si>
+    <t>g_w409798382-765_IND-w477691456-765_IND</t>
+  </si>
+  <si>
+    <t>g_w409798382-765_IND-w97392607-765_IND</t>
+  </si>
+  <si>
+    <t>e_w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN267-765_IND</t>
+  </si>
+  <si>
+    <t>g_w417569420-765_IND-IN267-765_IND</t>
+  </si>
+  <si>
+    <t>g_w417569420-765_IND-IN73-765_IND</t>
+  </si>
+  <si>
+    <t>g_w417569420-765_IND-w781425567-765_IND</t>
+  </si>
+  <si>
+    <t>e_w420797421-765_IND</t>
+  </si>
+  <si>
+    <t>g_w420797421-765_IND-IN135-765_IND</t>
+  </si>
+  <si>
+    <t>g_w420797421-765_IND-w105373531-765_IND</t>
+  </si>
+  <si>
+    <t>g_w420797421-765_IND-w1329624553-765_IND</t>
+  </si>
+  <si>
+    <t>g_w420797421-765_IND-w417569420-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425101516-765_IND</t>
+  </si>
+  <si>
+    <t>g_w420797421-765_IND-w425101516-765_IND</t>
+  </si>
+  <si>
+    <t>e_w422204218-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN312-765_IND</t>
+  </si>
+  <si>
+    <t>g_w422204218-765_IND-IN312-765_IND</t>
+  </si>
+  <si>
+    <t>g_w423702239-765_IND-IN295-765_IND</t>
+  </si>
+  <si>
+    <t>g_w425101516-765_IND-IN171-765_IND</t>
+  </si>
+  <si>
+    <t>g_w425101516-765_IND-IN267-765_IND</t>
+  </si>
+  <si>
+    <t>e_w425401901-765_IND</t>
+  </si>
+  <si>
+    <t>g_w425401901-765_IND-w386153973-765_IND</t>
+  </si>
+  <si>
+    <t>e_w429459345-765_IND</t>
+  </si>
+  <si>
+    <t>g_w429459345-765_IND-w492377703-765_IND</t>
+  </si>
+  <si>
+    <t>g_w439006823-400_IND-w374367235-400_IND</t>
+  </si>
+  <si>
+    <t>g_w439006823-400_IND-w375941438-400_IND</t>
+  </si>
+  <si>
+    <t>e_w453513742-765_IND</t>
+  </si>
+  <si>
+    <t>g_w453513742-765_IND-IN642-765_IND</t>
+  </si>
+  <si>
+    <t>g_w453513742-765_IND-IN659-765_IND</t>
+  </si>
+  <si>
+    <t>e_w465787206-400_IND</t>
+  </si>
+  <si>
+    <t>g_w465787206-400_IND-w239498664-400_IND</t>
+  </si>
+  <si>
+    <t>e_w466424134-765_IND</t>
+  </si>
+  <si>
+    <t>g_w466424134-765_IND-w201845280-765_IND</t>
+  </si>
+  <si>
+    <t>e_w473902678-765_IND</t>
+  </si>
+  <si>
+    <t>g_w473902678-765_IND-IN642-765_IND</t>
+  </si>
+  <si>
+    <t>g_w477691456-765_IND-IN412-765_IND</t>
+  </si>
+  <si>
+    <t>e_w196563905-765_IND</t>
+  </si>
+  <si>
+    <t>g_w477691456-765_IND-w196563905-765_IND</t>
+  </si>
+  <si>
+    <t>g_w477691456-765_IND-w328548895-765_IND</t>
+  </si>
+  <si>
+    <t>g_w485873934-400_IND-w92360278-400_IND</t>
+  </si>
+  <si>
+    <t>e_w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>g_w485873968-400_IND-w205942950-400_IND</t>
+  </si>
+  <si>
+    <t>e_w506461670-765_IND</t>
+  </si>
+  <si>
+    <t>g_w506461670-765_IND-IN539-765_IND</t>
+  </si>
+  <si>
+    <t>g_w506461670-765_IND-w311933111-765_IND</t>
+  </si>
+  <si>
+    <t>e_w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>g_w506461670-765_IND-w840600239-765_IND</t>
+  </si>
+  <si>
+    <t>e_w50885643-400_IND</t>
+  </si>
+  <si>
+    <t>g_w50885643-400_IND-IN285-400_IND</t>
+  </si>
+  <si>
+    <t>e_w92994753-400_IND</t>
+  </si>
+  <si>
+    <t>g_w50885643-400_IND-w92994753-400_IND</t>
+  </si>
+  <si>
+    <t>e_w96821783-400_IND</t>
+  </si>
+  <si>
+    <t>g_w50885643-400_IND-w96821783-400_IND</t>
+  </si>
+  <si>
+    <t>e_w50885643-765_IND</t>
+  </si>
+  <si>
+    <t>g_w50885643-765_IND-IN300-765_IND</t>
+  </si>
+  <si>
+    <t>g_w50885643-765_IND-w209806624-765_IND</t>
+  </si>
+  <si>
+    <t>g_w50885643-765_IND-w311103617-765_IND</t>
+  </si>
+  <si>
+    <t>e_w521570801-765_IND</t>
+  </si>
+  <si>
+    <t>g_w521570801-765_IND-w354062412-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN155-400_IND</t>
+  </si>
+  <si>
+    <t>g_w526897229-400_IND-IN155-400_IND</t>
+  </si>
+  <si>
+    <t>e_w551402699-765_IND</t>
+  </si>
+  <si>
+    <t>g_w551402699-765_IND-IN135-765_IND</t>
+  </si>
+  <si>
+    <t>g_w551402699-765_IND-IN136-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN140-765_IND</t>
+  </si>
+  <si>
+    <t>g_w551402699-765_IND-IN140-765_IND</t>
+  </si>
+  <si>
+    <t>g_w551402699-765_IND-w607439318-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1044735753-400_IND</t>
+  </si>
+  <si>
+    <t>g_w577176545-400_IND-w1044735753-400_IND</t>
+  </si>
+  <si>
+    <t>e_w608461884-765_IND</t>
+  </si>
+  <si>
+    <t>g_w608461884-765_IND-w293597835-765_IND</t>
+  </si>
+  <si>
+    <t>g_w631917408-765_IND-w369866141-765_IND</t>
+  </si>
+  <si>
+    <t>g_w654736039-765_IND-w372701897-765_IND</t>
+  </si>
+  <si>
+    <t>e_w655683221-765_IND</t>
+  </si>
+  <si>
+    <t>g_w655683221-765_IND-w631917408-765_IND</t>
+  </si>
+  <si>
+    <t>g_w655683221-765_IND-w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>g_w686891085-765_IND-w654736039-765_IND</t>
+  </si>
+  <si>
+    <t>e_w688672711-765_IND</t>
+  </si>
+  <si>
+    <t>g_w688672711-765_IND-w1078426593-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1336628403-765_IND</t>
+  </si>
+  <si>
+    <t>g_w688672711-765_IND-w1336628403-765_IND</t>
+  </si>
+  <si>
+    <t>g_w688672711-765_IND-w688672798-765_IND</t>
+  </si>
+  <si>
+    <t>e_w759521252-765_IND</t>
+  </si>
+  <si>
+    <t>g_w759521252-765_IND-w248385304-765_IND</t>
+  </si>
+  <si>
+    <t>e_w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>g_w759521252-765_IND-w793144832-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN160-765_IND</t>
+  </si>
+  <si>
+    <t>g_w781425567-765_IND-IN160-765_IND</t>
+  </si>
+  <si>
+    <t>e_IN167-765_IND</t>
+  </si>
+  <si>
+    <t>g_w781425567-765_IND-IN167-765_IND</t>
+  </si>
+  <si>
+    <t>g_w781425567-765_IND-w422204218-765_IND</t>
+  </si>
+  <si>
+    <t>g_w801704865-765_IND-w466424134-765_IND</t>
+  </si>
+  <si>
+    <t>g_w840600239-765_IND-w1207477934-765_IND</t>
+  </si>
+  <si>
+    <t>g_w840600239-765_IND-w514344408-765_IND</t>
+  </si>
+  <si>
+    <t>g_w840600239-765_IND-w608461884-765_IND</t>
+  </si>
+  <si>
+    <t>e_w910151268-765_IND</t>
+  </si>
+  <si>
+    <t>e_w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>g_w910151268-765_IND-w1074489047-765_IND</t>
+  </si>
+  <si>
+    <t>g_w910151268-765_IND-w751947947-765_IND</t>
+  </si>
+  <si>
+    <t>g_w923365745-765_IND-IN684-765_IND</t>
+  </si>
+  <si>
+    <t>e_w923418232-400_IND</t>
+  </si>
+  <si>
+    <t>g_w923418232-400_IND-w97392607-400_IND</t>
+  </si>
+  <si>
+    <t>e_IN179-400_IND</t>
+  </si>
+  <si>
+    <t>g_w92360278-400_IND-IN179-400_IND</t>
+  </si>
+  <si>
+    <t>g_w92360278-400_IND-w96821783-400_IND</t>
+  </si>
+  <si>
+    <t>g_w92994753-400_IND-IN285-400_IND</t>
+  </si>
+  <si>
+    <t>g_w92994753-400_IND-IN286-400_IND</t>
+  </si>
+  <si>
+    <t>g_w92994753-400_IND-w1044735753-400_IND</t>
+  </si>
+  <si>
+    <t>g_w92994753-400_IND-w1341647644-400_IND</t>
+  </si>
+  <si>
+    <t>g_w93160503-400_IND-IN320-400_IND</t>
+  </si>
+  <si>
+    <t>g_w93160503-400_IND-IN339-400_IND</t>
+  </si>
+  <si>
+    <t>g_w93160503-400_IND-w116541259-400_IND</t>
+  </si>
+  <si>
+    <t>g_w93160503-400_IND-w92360278-400_IND</t>
+  </si>
+  <si>
+    <t>g_w94199110-400_IND-IN286-400_IND</t>
+  </si>
+  <si>
+    <t>g_w96821783-400_IND-IN325-400_IND</t>
+  </si>
+  <si>
+    <t>e_w149822703-400_IND</t>
+  </si>
+  <si>
+    <t>g_w96821783-400_IND-w149822703-400_IND</t>
+  </si>
+  <si>
+    <t>g_w96821783-400_IND-w209806650-400_IND</t>
+  </si>
+  <si>
+    <t>e_w409798382-400_IND</t>
+  </si>
+  <si>
+    <t>g_w96821783-400_IND-w409798382-400_IND</t>
+  </si>
+  <si>
+    <t>g_w96821783-400_IND-w485873968-400_IND</t>
+  </si>
+  <si>
+    <t>g_w96821783-400_IND-w93160503-400_IND</t>
+  </si>
+  <si>
+    <t>g_w97392607-400_IND-IN317-400_IND</t>
+  </si>
+  <si>
+    <t>g_w97392607-400_IND-w96821783-400_IND</t>
+  </si>
+  <si>
+    <t>g_w97392607-765_IND-w209806624-765_IND</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -3055,7 +3058,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3110,39 +3113,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -3194,7 +3197,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -3305,6 +3308,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -3313,13 +3323,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -3384,38 +3387,18 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122414A6-0AFE-4930-AF1F-C42496162499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E5FAE4-154A-4161-89F4-C6B4FA72EACE}">
   <dimension ref="B3:L417"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0F930A3-7DF7-4374-9D45-AF2EE656AD6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{326F14BF-112A-4616-97C6-8A5DABBDC245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C4291C1A-BBC5-441C-94E6-EAEDEA9195AE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A2438699-AD72-43C3-87A0-84B3D37746CF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3398,7 +3398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E5FAE4-154A-4161-89F4-C6B4FA72EACE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52E450E0-CD1A-45A2-8B5F-6C255DEA0979}">
   <dimension ref="B3:L417"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{326F14BF-112A-4616-97C6-8A5DABBDC245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBB45923-81F2-4729-8BD1-FA591D6BD40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A2438699-AD72-43C3-87A0-84B3D37746CF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{554DEDF0-09F6-4A88-86D8-A4C86EDC2557}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3398,7 +3398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52E450E0-CD1A-45A2-8B5F-6C255DEA0979}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5215836-C518-4CC9-B809-DBDF9FE7B8B9}">
   <dimension ref="B3:L417"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBB45923-81F2-4729-8BD1-FA591D6BD40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16AB1479-9DB7-4984-B669-39635E826D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{554DEDF0-09F6-4A88-86D8-A4C86EDC2557}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{16F27083-F74E-4BF4-9A8D-F7581859C490}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3058,7 +3058,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3113,39 +3113,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -3197,7 +3197,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -3308,13 +3308,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -3323,6 +3316,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -3387,18 +3387,38 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5215836-C518-4CC9-B809-DBDF9FE7B8B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D3EB094-1978-4388-B94F-5B577B15D0A3}">
   <dimension ref="B3:L417"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16AB1479-9DB7-4984-B669-39635E826D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E43E6B1D-6B8C-4B84-9460-796291C14E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{16F27083-F74E-4BF4-9A8D-F7581859C490}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{571DA51D-4F7A-41C3-93E5-22B82B56CD5A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -3418,7 +3418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D3EB094-1978-4388-B94F-5B577B15D0A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8674CC91-CC62-4531-80F0-6377C4515FEA}">
   <dimension ref="B3:L417"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
